--- a/experiment_stimuli/Stims_full_old/sentence_judgment_stimuli.xlsx
+++ b/experiment_stimuli/Stims_full_old/sentence_judgment_stimuli.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Frances\Desktop\sdt\experiment_stimuli\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Frances\Desktop\lab\sdtWhole\experiment_stimuli\Stims_full_old\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3DFBBB1-7EEA-4CDE-8A07-8A9B8B4D74FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A7E164F-B8BC-452C-B1A8-C7561545BE16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12432" xr2:uid="{0528E85B-A8B2-41D5-939D-055D1CD16C2D}"/>
   </bookViews>
@@ -225,9 +225,6 @@
     <t>The friend's greeting was a hug.</t>
   </si>
   <si>
-    <t>His gait was a mild limp.</t>
-  </si>
-  <si>
     <t>The dance was a fast polka.</t>
   </si>
   <si>
@@ -291,9 +288,6 @@
     <t>The weather warning was a slide.</t>
   </si>
   <si>
-    <t>The man was an upright vacuum.</t>
-  </si>
-  <si>
     <t>The startling sound was a sky.</t>
   </si>
   <si>
@@ -312,9 +306,6 @@
     <t>The child's favorite was less preferred.</t>
   </si>
   <si>
-    <t>The sun is a familiar melody.</t>
-  </si>
-  <si>
     <t>The small gadget was a mountain.</t>
   </si>
   <si>
@@ -336,9 +327,6 @@
     <t>The blank paper was a catapult.</t>
   </si>
   <si>
-    <t>The submarine's weapon was a sloth.</t>
-  </si>
-  <si>
     <t>The tree was a local stream.</t>
   </si>
   <si>
@@ -366,9 +354,6 @@
     <t>The desert storm was a donut.</t>
   </si>
   <si>
-    <t>The yellow pen was a bullet.</t>
-  </si>
-  <si>
     <t>The new paving was a teeter-totter.</t>
   </si>
   <si>
@@ -532,6 +517,21 @@
   </si>
   <si>
     <t>Stimuli_type</t>
+  </si>
+  <si>
+    <t>The submarine weapon was a giraffe.</t>
+  </si>
+  <si>
+    <t>The man was an upright pencil.</t>
+  </si>
+  <si>
+    <t>His walk was a mild limp.</t>
+  </si>
+  <si>
+    <t>The oak tree was a bullet.</t>
+  </si>
+  <si>
+    <t>The tune is a familiar pen.</t>
   </si>
 </sst>
 </file>
@@ -944,19 +944,19 @@
   <sheetData>
     <row r="1" spans="1:26" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="F1" s="1"/>
       <c r="G1" s="5"/>
@@ -991,7 +991,7 @@
         <v>1</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="E2" s="5" t="b">
         <v>1</v>
@@ -1015,7 +1015,7 @@
         <v>11</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="E3" s="5" t="b">
         <v>1</v>
@@ -1039,7 +1039,7 @@
         <v>21</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="E4" s="5" t="b">
         <v>1</v>
@@ -1063,7 +1063,7 @@
         <v>31</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="E5" s="5" t="b">
         <v>1</v>
@@ -1087,7 +1087,7 @@
         <v>41</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="E6" s="5" t="b">
         <v>1</v>
@@ -1111,7 +1111,7 @@
         <v>51</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="E7" s="5" t="b">
         <v>1</v>
@@ -1135,7 +1135,7 @@
         <v>61</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="E8" s="5" t="b">
         <v>1</v>
@@ -1156,10 +1156,10 @@
         <v>0</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="E9" s="5" t="b">
         <v>1</v>
@@ -1177,10 +1177,10 @@
         <v>1</v>
       </c>
       <c r="B10" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="C10" s="2" t="s">
         <v>81</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>82</v>
       </c>
       <c r="D10" s="1">
         <v>1</v>
@@ -1201,10 +1201,10 @@
         <v>1</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D11" s="2">
         <v>2</v>
@@ -1225,10 +1225,10 @@
         <v>1</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="D12" s="1">
         <v>1</v>
@@ -1249,10 +1249,10 @@
         <v>1</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="D13" s="2">
         <v>2</v>
@@ -1273,13 +1273,13 @@
         <v>1</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="E14" s="5" t="b">
         <v>0</v>
@@ -1297,13 +1297,13 @@
         <v>1</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="E15" s="5" t="b">
         <v>0</v>
@@ -1321,13 +1321,13 @@
         <v>1</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="E16" s="5" t="b">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="E17" s="5" t="b">
         <v>0</v>
@@ -1375,7 +1375,7 @@
         <v>2</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="E18" s="5" t="b">
         <v>1</v>
@@ -1392,7 +1392,7 @@
         <v>12</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="E19" s="5" t="b">
         <v>1</v>
@@ -1409,7 +1409,7 @@
         <v>22</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="E20" s="5" t="b">
         <v>1</v>
@@ -1426,7 +1426,7 @@
         <v>32</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="E21" s="5" t="b">
         <v>1</v>
@@ -1443,7 +1443,7 @@
         <v>42</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="E22" s="5" t="b">
         <v>1</v>
@@ -1460,7 +1460,7 @@
         <v>52</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="E23" s="5" t="b">
         <v>1</v>
@@ -1477,7 +1477,7 @@
         <v>62</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="E24" s="5" t="b">
         <v>1</v>
@@ -1491,10 +1491,10 @@
         <v>0</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="E25" s="5" t="b">
         <v>1</v>
@@ -1505,10 +1505,10 @@
         <v>2</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D26" s="2">
         <v>2</v>
@@ -1522,10 +1522,10 @@
         <v>2</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="D27" s="1">
         <v>1</v>
@@ -1539,10 +1539,10 @@
         <v>2</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>103</v>
+        <v>164</v>
       </c>
       <c r="D28" s="2">
         <v>2</v>
@@ -1556,10 +1556,10 @@
         <v>2</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>113</v>
+        <v>167</v>
       </c>
       <c r="D29" s="2">
         <v>1</v>
@@ -1573,13 +1573,13 @@
         <v>2</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="E30" s="5" t="b">
         <v>0</v>
@@ -1590,13 +1590,13 @@
         <v>2</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="E31" s="5" t="b">
         <v>0</v>
@@ -1607,13 +1607,13 @@
         <v>2</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="E32" s="5" t="b">
         <v>0</v>
@@ -1624,13 +1624,13 @@
         <v>2</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="E33" s="5" t="b">
         <v>0</v>
@@ -1647,7 +1647,7 @@
         <v>3</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="E34" s="5" t="b">
         <v>1</v>
@@ -1664,7 +1664,7 @@
         <v>13</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="E35" s="5" t="b">
         <v>1</v>
@@ -1681,7 +1681,7 @@
         <v>23</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="E36" s="5" t="b">
         <v>1</v>
@@ -1698,7 +1698,7 @@
         <v>33</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="E37" s="5" t="b">
         <v>1</v>
@@ -1715,7 +1715,7 @@
         <v>43</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="E38" s="5" t="b">
         <v>1</v>
@@ -1732,7 +1732,7 @@
         <v>53</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="E39" s="5" t="b">
         <v>1</v>
@@ -1749,7 +1749,7 @@
         <v>63</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="E40" s="5" t="b">
         <v>1</v>
@@ -1763,10 +1763,10 @@
         <v>0</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="E41" s="5" t="b">
         <v>1</v>
@@ -1777,10 +1777,10 @@
         <v>3</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D42" s="2">
         <v>2</v>
@@ -1794,10 +1794,10 @@
         <v>3</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="D43" s="2">
         <v>2</v>
@@ -1811,10 +1811,10 @@
         <v>3</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="D44" s="1">
         <v>1</v>
@@ -1828,10 +1828,10 @@
         <v>3</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="D45" s="2">
         <v>1</v>
@@ -1845,13 +1845,13 @@
         <v>3</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="E46" s="5" t="b">
         <v>0</v>
@@ -1862,13 +1862,13 @@
         <v>3</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="E47" s="5" t="b">
         <v>0</v>
@@ -1879,13 +1879,13 @@
         <v>3</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="E48" s="5" t="b">
         <v>0</v>
@@ -1896,13 +1896,13 @@
         <v>3</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="E49" s="5" t="b">
         <v>0</v>
@@ -1919,7 +1919,7 @@
         <v>4</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="E50" s="5" t="b">
         <v>1</v>
@@ -1936,7 +1936,7 @@
         <v>14</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="E51" s="5" t="b">
         <v>1</v>
@@ -1953,7 +1953,7 @@
         <v>24</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="E52" s="5" t="b">
         <v>1</v>
@@ -1970,7 +1970,7 @@
         <v>34</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="E53" s="5" t="b">
         <v>1</v>
@@ -1987,7 +1987,7 @@
         <v>44</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="E54" s="5" t="b">
         <v>1</v>
@@ -2004,7 +2004,7 @@
         <v>54</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="E55" s="5" t="b">
         <v>1</v>
@@ -2021,7 +2021,7 @@
         <v>64</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="E56" s="5" t="b">
         <v>1</v>
@@ -2035,10 +2035,10 @@
         <v>0</v>
       </c>
       <c r="C57" s="5" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="E57" s="5" t="b">
         <v>1</v>
@@ -2049,10 +2049,10 @@
         <v>4</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D58" s="1">
         <v>1</v>
@@ -2066,10 +2066,10 @@
         <v>4</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>95</v>
+        <v>168</v>
       </c>
       <c r="D59" s="1">
         <v>1</v>
@@ -2083,10 +2083,10 @@
         <v>4</v>
       </c>
       <c r="B60" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="D60" s="1">
         <v>2</v>
@@ -2100,10 +2100,10 @@
         <v>4</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="D61" s="1">
         <v>2</v>
@@ -2117,13 +2117,13 @@
         <v>4</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="E62" s="5" t="b">
         <v>0</v>
@@ -2134,13 +2134,13 @@
         <v>4</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="E63" s="5" t="b">
         <v>0</v>
@@ -2151,13 +2151,13 @@
         <v>4</v>
       </c>
       <c r="B64" s="5" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="E64" s="5" t="b">
         <v>0</v>
@@ -2168,13 +2168,13 @@
         <v>4</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="E65" s="5" t="b">
         <v>0</v>
@@ -2191,7 +2191,7 @@
         <v>5</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="E66" s="5" t="b">
         <v>1</v>
@@ -2208,7 +2208,7 @@
         <v>15</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="E67" s="5" t="b">
         <v>1</v>
@@ -2225,7 +2225,7 @@
         <v>25</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="E68" s="5" t="b">
         <v>1</v>
@@ -2242,7 +2242,7 @@
         <v>35</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="E69" s="5" t="b">
         <v>1</v>
@@ -2259,7 +2259,7 @@
         <v>45</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="E70" s="5" t="b">
         <v>1</v>
@@ -2276,7 +2276,7 @@
         <v>55</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="E71" s="5" t="b">
         <v>1</v>
@@ -2293,7 +2293,7 @@
         <v>65</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="E72" s="5" t="b">
         <v>1</v>
@@ -2307,10 +2307,10 @@
         <v>0</v>
       </c>
       <c r="C73" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="E73" s="5" t="b">
         <v>1</v>
@@ -2321,10 +2321,10 @@
         <v>5</v>
       </c>
       <c r="B74" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D74" s="1">
         <v>1</v>
@@ -2338,10 +2338,10 @@
         <v>5</v>
       </c>
       <c r="B75" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="D75" s="2">
         <v>2</v>
@@ -2355,10 +2355,10 @@
         <v>5</v>
       </c>
       <c r="B76" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="D76" s="2">
         <v>2</v>
@@ -2372,10 +2372,10 @@
         <v>5</v>
       </c>
       <c r="B77" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="D77" s="2">
         <v>1</v>
@@ -2389,13 +2389,13 @@
         <v>5</v>
       </c>
       <c r="B78" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="C78" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="C78" s="2" t="s">
-        <v>127</v>
-      </c>
       <c r="D78" s="2" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="E78" s="5" t="b">
         <v>0</v>
@@ -2406,13 +2406,13 @@
         <v>5</v>
       </c>
       <c r="B79" s="5" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="E79" s="5" t="b">
         <v>0</v>
@@ -2423,13 +2423,13 @@
         <v>5</v>
       </c>
       <c r="B80" s="5" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="E80" s="5" t="b">
         <v>0</v>
@@ -2440,13 +2440,13 @@
         <v>5</v>
       </c>
       <c r="B81" s="5" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="E81" s="5" t="b">
         <v>0</v>
@@ -2463,7 +2463,7 @@
         <v>6</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="E82" s="5" t="b">
         <v>1</v>
@@ -2480,7 +2480,7 @@
         <v>16</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="E83" s="5" t="b">
         <v>1</v>
@@ -2497,7 +2497,7 @@
         <v>26</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="E84" s="5" t="b">
         <v>1</v>
@@ -2514,7 +2514,7 @@
         <v>36</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="E85" s="5" t="b">
         <v>1</v>
@@ -2531,7 +2531,7 @@
         <v>46</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="E86" s="5" t="b">
         <v>1</v>
@@ -2548,7 +2548,7 @@
         <v>56</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="E87" s="5" t="b">
         <v>1</v>
@@ -2562,10 +2562,10 @@
         <v>0</v>
       </c>
       <c r="C88" s="5" t="s">
-        <v>66</v>
+        <v>166</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="E88" s="5" t="b">
         <v>1</v>
@@ -2579,10 +2579,10 @@
         <v>0</v>
       </c>
       <c r="C89" s="5" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="E89" s="5" t="b">
         <v>1</v>
@@ -2593,10 +2593,10 @@
         <v>6</v>
       </c>
       <c r="B90" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D90" s="2">
         <v>2</v>
@@ -2610,10 +2610,10 @@
         <v>6</v>
       </c>
       <c r="B91" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="D91" s="1">
         <v>1</v>
@@ -2627,10 +2627,10 @@
         <v>6</v>
       </c>
       <c r="B92" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="D92" s="1">
         <v>1</v>
@@ -2644,10 +2644,10 @@
         <v>6</v>
       </c>
       <c r="B93" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="D93" s="2">
         <v>2</v>
@@ -2661,13 +2661,13 @@
         <v>6</v>
       </c>
       <c r="B94" s="5" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="E94" s="5" t="b">
         <v>0</v>
@@ -2678,13 +2678,13 @@
         <v>6</v>
       </c>
       <c r="B95" s="5" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="E95" s="5" t="b">
         <v>0</v>
@@ -2695,13 +2695,13 @@
         <v>6</v>
       </c>
       <c r="B96" s="5" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="E96" s="5" t="b">
         <v>0</v>
@@ -2712,13 +2712,13 @@
         <v>6</v>
       </c>
       <c r="B97" s="5" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="E97" s="5" t="b">
         <v>0</v>
@@ -2735,7 +2735,7 @@
         <v>7</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="E98" s="5" t="b">
         <v>1</v>
@@ -2752,7 +2752,7 @@
         <v>17</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="E99" s="5" t="b">
         <v>1</v>
@@ -2769,7 +2769,7 @@
         <v>27</v>
       </c>
       <c r="D100" s="2" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="E100" s="5" t="b">
         <v>1</v>
@@ -2786,7 +2786,7 @@
         <v>37</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="E101" s="5" t="b">
         <v>1</v>
@@ -2803,7 +2803,7 @@
         <v>47</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="E102" s="5" t="b">
         <v>1</v>
@@ -2820,7 +2820,7 @@
         <v>57</v>
       </c>
       <c r="D103" s="2" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="E103" s="5" t="b">
         <v>1</v>
@@ -2834,10 +2834,10 @@
         <v>0</v>
       </c>
       <c r="C104" s="5" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D104" s="2" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="E104" s="5" t="b">
         <v>1</v>
@@ -2851,10 +2851,10 @@
         <v>0</v>
       </c>
       <c r="C105" s="5" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D105" s="2" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="E105" s="5" t="b">
         <v>1</v>
@@ -2865,10 +2865,10 @@
         <v>7</v>
       </c>
       <c r="B106" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>88</v>
+        <v>165</v>
       </c>
       <c r="D106" s="1">
         <v>1</v>
@@ -2882,10 +2882,10 @@
         <v>7</v>
       </c>
       <c r="B107" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="D107" s="2">
         <v>2</v>
@@ -2899,10 +2899,10 @@
         <v>7</v>
       </c>
       <c r="B108" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="D108" s="1">
         <v>1</v>
@@ -2916,10 +2916,10 @@
         <v>7</v>
       </c>
       <c r="B109" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="D109" s="2">
         <v>2</v>
@@ -2933,13 +2933,13 @@
         <v>7</v>
       </c>
       <c r="B110" s="5" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="D110" s="2" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="E110" s="5" t="b">
         <v>0</v>
@@ -2950,13 +2950,13 @@
         <v>7</v>
       </c>
       <c r="B111" s="5" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="D111" s="2" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="E111" s="5" t="b">
         <v>0</v>
@@ -2967,13 +2967,13 @@
         <v>7</v>
       </c>
       <c r="B112" s="5" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="C112" s="2" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="D112" s="2" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="E112" s="5" t="b">
         <v>0</v>
@@ -2984,13 +2984,13 @@
         <v>7</v>
       </c>
       <c r="B113" s="5" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="C113" s="2" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="D113" s="2" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="E113" s="5" t="b">
         <v>0</v>
@@ -3007,7 +3007,7 @@
         <v>8</v>
       </c>
       <c r="D114" s="2" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="E114" s="5" t="b">
         <v>1</v>
@@ -3024,7 +3024,7 @@
         <v>18</v>
       </c>
       <c r="D115" s="2" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="E115" s="5" t="b">
         <v>1</v>
@@ -3041,7 +3041,7 @@
         <v>28</v>
       </c>
       <c r="D116" s="2" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="E116" s="5" t="b">
         <v>1</v>
@@ -3058,7 +3058,7 @@
         <v>38</v>
       </c>
       <c r="D117" s="2" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="E117" s="5" t="b">
         <v>1</v>
@@ -3075,7 +3075,7 @@
         <v>48</v>
       </c>
       <c r="D118" s="2" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="E118" s="5" t="b">
         <v>1</v>
@@ -3092,7 +3092,7 @@
         <v>58</v>
       </c>
       <c r="D119" s="2" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="E119" s="5" t="b">
         <v>1</v>
@@ -3106,10 +3106,10 @@
         <v>0</v>
       </c>
       <c r="C120" s="5" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D120" s="2" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="E120" s="5" t="b">
         <v>1</v>
@@ -3123,10 +3123,10 @@
         <v>0</v>
       </c>
       <c r="C121" s="5" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D121" s="2" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="E121" s="5" t="b">
         <v>1</v>
@@ -3137,10 +3137,10 @@
         <v>8</v>
       </c>
       <c r="B122" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="D122" s="2">
         <v>2</v>
@@ -3154,10 +3154,10 @@
         <v>8</v>
       </c>
       <c r="B123" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C123" s="2" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="D123" s="1">
         <v>1</v>
@@ -3171,10 +3171,10 @@
         <v>8</v>
       </c>
       <c r="B124" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C124" s="2" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="D124" s="2">
         <v>2</v>
@@ -3188,10 +3188,10 @@
         <v>8</v>
       </c>
       <c r="B125" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C125" s="2" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="D125" s="2">
         <v>1</v>
@@ -3205,13 +3205,13 @@
         <v>8</v>
       </c>
       <c r="B126" s="5" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="C126" s="2" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="D126" s="2" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="E126" s="5" t="b">
         <v>0</v>
@@ -3222,13 +3222,13 @@
         <v>8</v>
       </c>
       <c r="B127" s="5" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="C127" s="2" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="D127" s="2" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="E127" s="5" t="b">
         <v>0</v>
@@ -3239,13 +3239,13 @@
         <v>8</v>
       </c>
       <c r="B128" s="5" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="C128" s="2" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="D128" s="2" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="E128" s="5" t="b">
         <v>0</v>
@@ -3256,13 +3256,13 @@
         <v>8</v>
       </c>
       <c r="B129" s="5" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="C129" s="2" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="D129" s="2" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="E129" s="5" t="b">
         <v>0</v>
@@ -3279,7 +3279,7 @@
         <v>9</v>
       </c>
       <c r="D130" s="2" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="E130" s="5" t="b">
         <v>1</v>
@@ -3296,7 +3296,7 @@
         <v>19</v>
       </c>
       <c r="D131" s="2" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="E131" s="5" t="b">
         <v>1</v>
@@ -3313,7 +3313,7 @@
         <v>29</v>
       </c>
       <c r="D132" s="2" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="E132" s="5" t="b">
         <v>1</v>
@@ -3330,7 +3330,7 @@
         <v>39</v>
       </c>
       <c r="D133" s="2" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="E133" s="5" t="b">
         <v>1</v>
@@ -3347,7 +3347,7 @@
         <v>49</v>
       </c>
       <c r="D134" s="2" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="E134" s="5" t="b">
         <v>1</v>
@@ -3364,7 +3364,7 @@
         <v>59</v>
       </c>
       <c r="D135" s="2" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="E135" s="5" t="b">
         <v>1</v>
@@ -3378,10 +3378,10 @@
         <v>0</v>
       </c>
       <c r="C136" s="5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D136" s="2" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="E136" s="5" t="b">
         <v>1</v>
@@ -3395,10 +3395,10 @@
         <v>0</v>
       </c>
       <c r="C137" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D137" s="2" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="E137" s="5" t="b">
         <v>1</v>
@@ -3409,10 +3409,10 @@
         <v>9</v>
       </c>
       <c r="B138" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C138" s="2" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="D138" s="2">
         <v>2</v>
@@ -3426,10 +3426,10 @@
         <v>9</v>
       </c>
       <c r="B139" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C139" s="2" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="D139" s="2">
         <v>2</v>
@@ -3443,10 +3443,10 @@
         <v>9</v>
       </c>
       <c r="B140" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C140" s="2" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="D140" s="1">
         <v>1</v>
@@ -3460,10 +3460,10 @@
         <v>9</v>
       </c>
       <c r="B141" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C141" s="2" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="D141" s="2">
         <v>1</v>
@@ -3477,13 +3477,13 @@
         <v>9</v>
       </c>
       <c r="B142" s="5" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="C142" s="2" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="D142" s="2" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="E142" s="5" t="b">
         <v>0</v>
@@ -3494,13 +3494,13 @@
         <v>9</v>
       </c>
       <c r="B143" s="5" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="C143" s="2" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="D143" s="2" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="E143" s="5" t="b">
         <v>0</v>
@@ -3511,13 +3511,13 @@
         <v>9</v>
       </c>
       <c r="B144" s="5" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="C144" s="2" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="D144" s="2" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="E144" s="5" t="b">
         <v>0</v>
@@ -3528,13 +3528,13 @@
         <v>9</v>
       </c>
       <c r="B145" s="5" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="C145" s="2" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="D145" s="2" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="E145" s="5" t="b">
         <v>0</v>
@@ -3551,7 +3551,7 @@
         <v>10</v>
       </c>
       <c r="D146" s="2" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="E146" s="5" t="b">
         <v>1</v>
@@ -3568,7 +3568,7 @@
         <v>20</v>
       </c>
       <c r="D147" s="2" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="E147" s="5" t="b">
         <v>1</v>
@@ -3585,7 +3585,7 @@
         <v>30</v>
       </c>
       <c r="D148" s="2" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="E148" s="5" t="b">
         <v>1</v>
@@ -3602,7 +3602,7 @@
         <v>40</v>
       </c>
       <c r="D149" s="2" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="E149" s="5" t="b">
         <v>1</v>
@@ -3619,7 +3619,7 @@
         <v>50</v>
       </c>
       <c r="D150" s="2" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="E150" s="5" t="b">
         <v>1</v>
@@ -3636,7 +3636,7 @@
         <v>60</v>
       </c>
       <c r="D151" s="2" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="E151" s="5" t="b">
         <v>1</v>
@@ -3650,10 +3650,10 @@
         <v>0</v>
       </c>
       <c r="C152" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D152" s="2" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="E152" s="5" t="b">
         <v>1</v>
@@ -3667,10 +3667,10 @@
         <v>0</v>
       </c>
       <c r="C153" s="5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D153" s="2" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="E153" s="5" t="b">
         <v>1</v>
@@ -3681,10 +3681,10 @@
         <v>10</v>
       </c>
       <c r="B154" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C154" s="2" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D154" s="1">
         <v>1</v>
@@ -3698,10 +3698,10 @@
         <v>10</v>
       </c>
       <c r="B155" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C155" s="2" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="D155" s="2">
         <v>2</v>
@@ -3715,10 +3715,10 @@
         <v>10</v>
       </c>
       <c r="B156" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C156" s="2" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="D156" s="2">
         <v>2</v>
@@ -3732,10 +3732,10 @@
         <v>10</v>
       </c>
       <c r="B157" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C157" s="2" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="D157" s="2">
         <v>1</v>
@@ -3749,13 +3749,13 @@
         <v>10</v>
       </c>
       <c r="B158" s="5" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="C158" s="2" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="D158" s="2" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="E158" s="5" t="b">
         <v>0</v>
@@ -3766,13 +3766,13 @@
         <v>10</v>
       </c>
       <c r="B159" s="5" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="C159" s="2" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="D159" s="2" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="E159" s="5" t="b">
         <v>0</v>
@@ -3783,13 +3783,13 @@
         <v>10</v>
       </c>
       <c r="B160" s="5" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="C160" s="2" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="D160" s="2" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="E160" s="5" t="b">
         <v>0</v>
@@ -3800,13 +3800,13 @@
         <v>10</v>
       </c>
       <c r="B161" s="5" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="C161" s="2" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="D161" s="2" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="E161" s="5" t="b">
         <v>0</v>
